--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1520">
   <si>
     <r>
       <t xml:space="preserve">行政長官</t>
@@ -112,7 +112,6 @@
     <r>
       <t xml:space="preserve">局長：雷子燊
 副局長：潘勁生
-副局長：---
 </t>
     </r>
   </si>
@@ -150,7 +149,6 @@
     <r>
       <t xml:space="preserve">局長：張作文
 副局長：吳海恩
-副局長：---
 </t>
     </r>
   </si>
@@ -248,8 +246,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">代局長：黃樂宜
-代副局長：楊寶琴
+      <t xml:space="preserve">局長：黃樂宜
+副局長：楊寶琴
 </t>
     </r>
   </si>
@@ -796,14 +794,13 @@
     <r>
       <t xml:space="preserve">局長：梁穎妍
 副局長：陳子健
-副局長：陳淑貞
 副局長：---
 </t>
     </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">政府資訊中心</t>
+      <t xml:space="preserve">政務服務資訊中心</t>
     </r>
   </si>
   <si>
@@ -1175,8 +1172,8 @@
   <si>
     <r>
       <t xml:space="preserve">行政管理委員會主席：高舒婷
-行政管理委員會副主席：江海莉
 行政管理委員會副主席：何志良
+行政管理委員會副主席：---
 </t>
     </r>
   </si>
@@ -1250,17 +1247,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">登記暨公證委員會</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2856 4225,（853）2859 5298</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2871 0445</t>
+      <t xml:space="preserve">登記及公證委員會</t>
     </r>
   </si>
   <si>
@@ -1280,12 +1267,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）8987 1515</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> info@caspdo.gov.mo</t>
+      <t xml:space="preserve">info@caspdo.gov.mo</t>
     </r>
   </si>
   <si>
@@ -1301,11 +1283,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門水坑尾街162號公共行政大樓22樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">（853）2871 8788</t>
     </r>
   </si>
@@ -1352,7 +1329,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">司長：---
+      <t xml:space="preserve">司長：吳惠嫻
 辦公室主任：羅志輝
 </t>
     </r>
@@ -1364,7 +1341,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">經濟財政司司長：---
+      <t xml:space="preserve">經濟財政司司長：吳惠嫻
 辦公室主任：羅志輝
 </t>
     </r>
@@ -1402,7 +1379,7 @@
   <si>
     <r>
       <t xml:space="preserve">局長：邱潤華
-副局長：鄭曉敏
+副局長：余雨生
 副局長：陳祖榮
 </t>
     </r>
@@ -1442,7 +1419,7 @@
     <r>
       <t xml:space="preserve">局長：何燕梅
 副局長：郭日海
-代副局長：譚麗霞
+副局長：譚麗霞
 </t>
     </r>
   </si>
@@ -1458,7 +1435,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）8599 5147，（853）8599 5181，（853）8599 5100</t>
+      <t xml:space="preserve">（853）8599 5147，（853）8599 5181</t>
     </r>
   </si>
   <si>
@@ -1468,7 +1445,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">代主任：朱奕聰
+      <t xml:space="preserve">主任：朱奕聰
 </t>
     </r>
   </si>
@@ -1542,9 +1519,9 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">局長：吳惠嫻
-副局長：廖志聰
+      <t xml:space="preserve">代局長：廖志聰
 副局長：李錫樵
+代副局長：黃朗平
 </t>
     </r>
   </si>
@@ -1665,201 +1642,164 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">統計暨普查局</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門宋玉生廣場411-417號皇朝廣場17樓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2872 8188</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2856 1884</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">info@dsec.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">http://www.dsec.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">代局長：黎嘉駿
+副局長：區家穎
+代副局長：馮炳傑
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">工商業發展基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2871 2552 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">行政管理委員會主席：邱潤華
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">汽車及航海保障基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2856 8288</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">行政管理委員會主席：黃善文
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">旅遊基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2831 5566，（853）2851 3355</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">行政管理委員會主席：文綺華
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">存款保障基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">勞動債權保障基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門馬揸度博士大馬路221-279號先進廣場勞工事務局總辦事處</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2871 7822</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2852 5934</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">info@fgcl.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">http://www.fgcl.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">行政管理委員會主席：陳元童
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">科學技術發展基金</t>
     </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門殷皇子大馬路 43 - 53A澳門廣場 8樓C座及 11樓K座</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2878 8777</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2878 8775,（853）2878 8776</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info@fdct.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">http://www.fdct.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">行政委員會主席：余雨生
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">統計暨普查局</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門宋玉生廣場411-417號皇朝廣場17樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2872 8188</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2856 1884</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info@dsec.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">http://www.dsec.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">局長：龐啓富
-副局長：黎嘉駿
-副局長：區家穎
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">消費者委員會</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門高士德大馬路 26號何鴻燊夫人大廈 4樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）8988 9315</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2830 7816 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info@consumer.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">http://www.consumer.gov.mo </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">主席：梁碧珊
-代副主席：余琴
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">工商業發展基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2871 2552 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">行政管理委員會主席：邱潤華
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">汽車及航海保障基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2856 8288</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">行政管理委員會主席：黃善文
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">旅遊基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2831 5566，（853）2851 3355</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">行政管理委員會主席：文綺華
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">存款保障基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">勞動債權保障基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門馬揸度博士大馬路221-279號先進廣場勞工事務局總辦事處</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2871 7822</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2852 5934</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info@fgcl.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">http://www.fgcl.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">行政管理委員會主席：陳元童
+      <t xml:space="preserve">科研資助查詢：澳門殷皇子大馬路43-53A澳門廣場11樓K座&lt;/br&gt;行政支援查詢：澳門南灣羅保博士街1至3號國際銀行大廈6樓行政及財政處</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">科研資助查詢：(853) 2878 8777 &lt;/br&gt;行政支援查詢：(853) 2888 2088</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">科研資助查詢：(853) 2878 8775 / 2878 8776 &lt;/br&gt;行政支援查詢：(853) 2871 2552</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">fdct@dsedt.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">https://fdct.dsedt.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">行政管理委員會主席：余雨生
 </t>
     </r>
   </si>
@@ -1915,9 +1855,9 @@
   <si>
     <r>
       <t xml:space="preserve">局長：梁文昌
-局長助理：魏瑞斌
 局長助理：梁文照
 局長助理：林俊生
+代局長助理：李日明
 金融情報辦公室主任：朱婉儀
 辦公室協調員：趙汝民
 金融情報辦公室副主任：馮婉琪
@@ -2000,8 +1940,10 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">代局長：伍素萍
-代副局長：鄭俊禧
+      <t xml:space="preserve">局長：伍素萍
+代副局長：江偉俊
+代副局長：黃劍虹
+代副局長：陳溥棠
 </t>
     </r>
   </si>
@@ -2023,12 +1965,12 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2831 2780 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">nar@pj.gov.mo</t>
+      <t xml:space="preserve">（853）2831 2780</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sfdtr@pj.gov.mo</t>
     </r>
   </si>
   <si>
@@ -2080,7 +2022,7 @@
     <r>
       <t xml:space="preserve">局長：王健
 副局長：張智宏
-代副局長：李龍傑
+副局長：李龍傑
 </t>
     </r>
   </si>
@@ -2117,8 +2059,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">局長：程况明
-副局長：李日明
+      <t xml:space="preserve">代局長：李昶文
+代副局長：呂錦雲
 </t>
     </r>
   </si>
@@ -2264,7 +2206,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">行政管理委員會主席：程况明
+      <t xml:space="preserve">行政管理委員會主席：李昶文
 </t>
     </r>
   </si>
@@ -2323,6 +2265,7 @@
   <si>
     <r>
       <t xml:space="preserve">行政管理委員會主席：伍素萍
+行政管理委員會副主席：江偉俊
 </t>
     </r>
   </si>
@@ -2464,9 +2407,9 @@
   <si>
     <r>
       <t xml:space="preserve">局長：龔志明
-副局長：丁少雄
 副局長：阮佩賢
 副局長：黃嘉祺
+代副局長：蔡敏芝
 </t>
     </r>
   </si>
@@ -2677,6 +2620,31 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">澳門演藝學院附屬教育中心</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門高士德大馬路14-16號</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2857 1230</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2852 3483</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">https://portal.dsedj.gov.mo/webdsejspace/cons/Inter_main_page.jsp</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">中葡職業技術學校</t>
     </r>
   </si>
@@ -2848,6 +2816,16 @@
   <si>
     <r>
       <t xml:space="preserve">http://www.eospv.k12.edu.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門演藝學院</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2857 1207</t>
     </r>
   </si>
   <si>
@@ -2890,45 +2868,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門演藝學院</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門演藝學院：澳門高士德大馬路14-16號
-舞蹈學校︰澳門路環紅荷路108號政府（路環）辦公大樓6樓
-音樂學校︰澳門和隆街35號（望德堂對面）
-戲劇學校：澳門友誼大馬路海景花園新安花園87 號U</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門演藝學院：（853）2857 1207 
-舞蹈學校：（853）2875 0562 
- 音樂學校：（853）2835 2766 
-戲劇學校：（853）2870 1588</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門演藝學院：（853）2852 3483 
-舞蹈學校：（853）2875 0568 
-音樂學校：（853）2835 2700 
-戲劇學校：（853）2870 1568</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info.cm@icm.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">http://www.cons.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">澳門檔案館</t>
     </r>
   </si>
@@ -3864,9 +3803,9 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">代局長：李詩靈
+      <t xml:space="preserve">局長：梁惠敏
+副局長：李詩靈
 副局長：鄭繼明
-副局長：---
 </t>
     </r>
   </si>
@@ -3905,7 +3844,7 @@
       <t xml:space="preserve">局長：羅奕龍
 副局長：鄭成業
 副局長：陳永華
-代副局長：戴華浩（仁伯爵綜合醫院代院長）
+副局長：戴華浩（仁伯爵綜合醫院院長）
 </t>
     </r>
   </si>
@@ -4511,10 +4450,10 @@
   <si>
     <r>
       <t xml:space="preserve">院長：劉正印
-副院長：李偉成
-副院長：李莉
+副院長：柳曉輝
+副院長：胡冰水
 副院長：孫國強
-職位等同副院長級別的人員：柳曉輝
+職位等同副院長級別的人員：趙穎
 職位等同副院長級別的人員：沈寧
 </t>
     </r>
@@ -4553,7 +4492,7 @@
     <r>
       <t xml:space="preserve">局長：韓衛
 副局長：許華寶
-副局長：鄧玉華
+副局長：丁少雄
 </t>
     </r>
   </si>
@@ -4951,7 +4890,7 @@
       <t xml:space="preserve">校長：周仲榮
 副校長：羅曼儀
 副校長：---
-秘書長：莫秀妍
+代秘書長：甄嘉瑩
 </t>
     </r>
   </si>
@@ -5026,7 +4965,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">行政管理委員會主席：李詩靈
+      <t xml:space="preserve">行政管理委員會主席：梁惠敏
 </t>
     </r>
   </si>
@@ -5474,8 +5413,8 @@
   <si>
     <r>
       <t xml:space="preserve">局長：鄭岳威
-副局長：李頴康
 副局長：莫垂道
+代副局長：雅永健
 </t>
     </r>
   </si>
@@ -6284,17 +6223,17 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）8398 4117 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2832 6744 </t>
+      <t xml:space="preserve">澳門南灣大馬路459號</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）8298 4117</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2832 6744</t>
     </r>
   </si>
   <si>
@@ -6317,28 +6256,38 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">澳門四月二十五日前地</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">（853）8398 4100</t>
     </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2832 6747 </t>
+      <t xml:space="preserve">（853）2832 6747</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">https://www.court.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">院長：盛銳敏
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">第一審法院</t>
     </r>
   </si>
   <si>
     <r>
       <t xml:space="preserve">http://www.court.gov.mo </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">院長：蔡武彬
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">第一審法院</t>
     </r>
   </si>
   <si>
@@ -6500,12 +6449,12 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門湖畔南街中國與葡語國家商貿合作服務平台綜合體辦公樓2樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）8398 4136</t>
+      <t xml:space="preserve">澳門龍嵩正街9-A號</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）8298 4136</t>
     </r>
   </si>
   <si>
@@ -6523,6 +6472,11 @@
   <si>
     <r>
       <t xml:space="preserve">推薦法官的獨立委員會</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
     </r>
   </si>
   <si>
@@ -6610,12 +6564,22 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">（853）2850 9183</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">檢察院駐中級法院辦事處</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">（853）2836 5214</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">檢察院駐中級法院辦事處</t>
     </r>
   </si>
   <si>
@@ -6954,17 +6918,22 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2885 0065 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2885 0083 </t>
+      <t xml:space="preserve">（853）2885 0065</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2885 0083</t>
     </r>
   </si>
   <si>
     <r>
       <t xml:space="preserve">csrmacau@macau.ctm.net</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">https://www.csrmacau.com.mo</t>
     </r>
   </si>
   <si>
@@ -7606,7 +7575,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門俾利喇街157號A</t>
+      <t xml:space="preserve">澳門俾利喇街157號A
+澳門路環紅荷路108號政府(路環)辦公大樓10樓</t>
     </r>
   </si>
   <si>
@@ -7632,10 +7602,10 @@
   <si>
     <r>
       <t xml:space="preserve">執行委員會主席：羅崇雯
-委員：馬錦強
 委員：袁泳貴
 委員：黃偉鴻
 委員：鄭光普
+委員：李從正
 </t>
     </r>
   </si>
@@ -7899,7 +7869,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">董事長：嚴肇基
+      <t xml:space="preserve">董事長：羅曼儀
 </t>
     </r>
   </si>
@@ -8015,6 +7985,34 @@
       <t xml:space="preserve">董事長：謝永強
 董事：譚致寧
 董事：陳祖榮
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">廣東橫琴粵澳深度合作區澳理大高等教育發展有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">珠海市橫琴港澳大道868號市民服務中心2號樓政務服務中心114室-3343（集中辦公區）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）8599 6765</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">mpuhed@mpu.edu.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">董事長：周仲榮
+董事：張詠藍
+董事：林逸文
 </t>
     </r>
   </si>
@@ -8355,7 +8353,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8596,7 +8594,6 @@
           <r>
             <t xml:space="preserve">局長：雷子燊
 副局長：潘勁生
-副局長：---
 </t>
           </r>
         </is>
@@ -8657,7 +8654,6 @@
           <r>
             <t xml:space="preserve">局長：張作文
 副局長：吳海恩
-副局長：---
 </t>
           </r>
         </is>
@@ -8827,8 +8823,8 @@
       <c r="H8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">代局長：黃樂宜
-代副局長：楊寶琴
+            <t xml:space="preserve">局長：黃樂宜
+副局長：楊寶琴
 </t>
           </r>
         </is>
@@ -9946,7 +9942,6 @@
           <r>
             <t xml:space="preserve">局長：梁穎妍
 副局長：陳子健
-副局長：陳淑貞
 副局長：---
 </t>
           </r>
@@ -9957,7 +9952,7 @@
       <c r="A28" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">政府資訊中心</t>
+            <t xml:space="preserve">政務服務資訊中心</t>
           </r>
         </is>
       </c>
@@ -10652,8 +10647,8 @@
         <is>
           <r>
             <t xml:space="preserve">行政管理委員會主席：高舒婷
-行政管理委員會副主席：江海莉
 行政管理委員會副主席：何志良
+行政管理委員會副主席：---
 </t>
           </r>
         </is>
@@ -10833,42 +10828,42 @@
       <c r="A43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">登記暨公證委員會</t>
+            <t xml:space="preserve">登記及公證委員會</t>
           </r>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門水坑尾街162號公共行政大樓15-20樓</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2856 4225,（853）2859 5298</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 0445</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@dsaj.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.dsaj.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -10905,14 +10900,14 @@
       <c r="D44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8987 1515</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"> info@caspdo.gov.mo</t>
+            <t xml:space="preserve">info@caspdo.gov.mo</t>
           </r>
         </is>
       </c>
@@ -10950,7 +10945,7 @@
       <c r="B45" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門水坑尾街162號公共行政大樓22樓</t>
+            <t xml:space="preserve">澳門水坑尾街162號公共行政大樓12樓</t>
           </r>
         </is>
       </c>
@@ -11051,7 +11046,7 @@
       <c r="H46" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">司長：---
+            <t xml:space="preserve">司長：吳惠嫻
 辦公室主任：羅志輝
 </t>
           </r>
@@ -11111,7 +11106,7 @@
       <c r="H47" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">經濟財政司司長：---
+            <t xml:space="preserve">經濟財政司司長：吳惠嫻
 辦公室主任：羅志輝
 </t>
           </r>
@@ -11172,7 +11167,7 @@
         <is>
           <r>
             <t xml:space="preserve">局長：邱潤華
-副局長：鄭曉敏
+副局長：余雨生
 副局長：陳祖榮
 </t>
           </r>
@@ -11235,7 +11230,7 @@
           <r>
             <t xml:space="preserve">局長：何燕梅
 副局長：郭日海
-代副局長：譚麗霞
+副局長：譚麗霞
 </t>
           </r>
         </is>
@@ -11259,7 +11254,7 @@
       <c r="C50" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8599 5147，（853）8599 5181，（853）8599 5100</t>
+            <t xml:space="preserve">（853）8599 5147，（853）8599 5181</t>
           </r>
         </is>
       </c>
@@ -11294,7 +11289,7 @@
       <c r="H50" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">代主任：朱奕聰
+            <t xml:space="preserve">主任：朱奕聰
 </t>
           </r>
         </is>
@@ -11414,9 +11409,9 @@
       <c r="H52" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">局長：吳惠嫻
-副局長：廖志聰
+            <t xml:space="preserve">代局長：廖志聰
 副局長：李錫樵
+代副局長：黃朗平
 </t>
           </r>
         </is>
@@ -11610,42 +11605,42 @@
       <c r="A56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">科學技術發展基金</t>
+            <t xml:space="preserve">統計暨普查局</t>
           </r>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門殷皇子大馬路 43 - 53A澳門廣場 8樓C座及 11樓K座</t>
+            <t xml:space="preserve">澳門宋玉生廣場411-417號皇朝廣場17樓</t>
           </r>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2878 8777</t>
+            <t xml:space="preserve">（853）2872 8188</t>
           </r>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2878 8775,（853）2878 8776</t>
+            <t xml:space="preserve">（853）2856 1884</t>
           </r>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@fdct.gov.mo</t>
+            <t xml:space="preserve">info@dsec.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.fdct.gov.mo</t>
+            <t xml:space="preserve">http://www.dsec.gov.mo</t>
           </r>
         </is>
       </c>
@@ -11659,7 +11654,9 @@
       <c r="H56" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政委員會主席：余雨生
+            <t xml:space="preserve">代局長：黎嘉駿
+副局長：區家穎
+代副局長：馮炳傑
 </t>
           </r>
         </is>
@@ -11669,42 +11666,42 @@
       <c r="A57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">統計暨普查局</t>
+            <t xml:space="preserve">工商業發展基金</t>
           </r>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門宋玉生廣場411-417號皇朝廣場17樓</t>
+            <t xml:space="preserve">澳門南灣羅保博士街1-3號國際銀行大廈6樓</t>
           </r>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2872 8188</t>
+            <t xml:space="preserve">（853）2888 2088</t>
           </r>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2856 1884</t>
+            <t xml:space="preserve">（853）2871 2552 </t>
           </r>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@dsec.gov.mo</t>
+            <t xml:space="preserve">info@dsedt.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.dsec.gov.mo</t>
+            <t xml:space="preserve">http://www.dsedt.gov.mo</t>
           </r>
         </is>
       </c>
@@ -11718,9 +11715,7 @@
       <c r="H57" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">局長：龐啓富
-副局長：黎嘉駿
-副局長：區家穎
+            <t xml:space="preserve">行政管理委員會主席：邱潤華
 </t>
           </r>
         </is>
@@ -11730,42 +11725,42 @@
       <c r="A58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">消費者委員會</t>
+            <t xml:space="preserve">汽車及航海保障基金</t>
           </r>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門高士德大馬路 26號何鴻燊夫人大廈 4樓</t>
+            <t xml:space="preserve">澳門東望洋斜巷24及26號</t>
           </r>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8988 9315</t>
+            <t xml:space="preserve">（853）2856 8288</t>
           </r>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2830 7816 </t>
+            <t xml:space="preserve">（853）2832 5432</t>
           </r>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@consumer.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.consumer.gov.mo </t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -11779,8 +11774,7 @@
       <c r="H58" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">主席：梁碧珊
-代副主席：余琴
+            <t xml:space="preserve">行政管理委員會主席：黃善文
 </t>
           </r>
         </is>
@@ -11790,42 +11784,42 @@
       <c r="A59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">工商業發展基金</t>
+            <t xml:space="preserve">旅遊基金</t>
           </r>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門南灣羅保博士街1-3號國際銀行大廈6樓</t>
+            <t xml:space="preserve">澳門新口岸宋玉生廣場335-341號獲多利大廈12樓</t>
           </r>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 2088</t>
+            <t xml:space="preserve">（853）2831 5566，（853）2851 3355</t>
           </r>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 2552 </t>
+            <t xml:space="preserve">（853）2851 0104</t>
           </r>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@dsedt.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.dsedt.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -11839,7 +11833,7 @@
       <c r="H59" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：邱潤華
+            <t xml:space="preserve">行政管理委員會主席：文綺華
 </t>
           </r>
         </is>
@@ -11849,7 +11843,7 @@
       <c r="A60" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">汽車及航海保障基金</t>
+            <t xml:space="preserve">存款保障基金</t>
           </r>
         </is>
       </c>
@@ -11908,42 +11902,42 @@
       <c r="A61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">旅遊基金</t>
+            <t xml:space="preserve">勞動債權保障基金</t>
           </r>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門新口岸宋玉生廣場335-341號獲多利大廈12樓</t>
+            <t xml:space="preserve">澳門馬揸度博士大馬路221-279號先進廣場勞工事務局總辦事處</t>
           </r>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2831 5566，（853）2851 3355</t>
+            <t xml:space="preserve">（853）2871 7822</t>
           </r>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2851 0104</t>
+            <t xml:space="preserve">（853）2852 5934</t>
           </r>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">info@fgcl.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">http://www.fgcl.gov.mo</t>
           </r>
         </is>
       </c>
@@ -11957,7 +11951,7 @@
       <c r="H61" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：文綺華
+            <t xml:space="preserve">行政管理委員會主席：陳元童
 </t>
           </r>
         </is>
@@ -11967,42 +11961,42 @@
       <c r="A62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">存款保障基金</t>
+            <t xml:space="preserve">科學技術發展基金</t>
           </r>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門東望洋斜巷24及26號</t>
+            <t xml:space="preserve">科研資助查詢：澳門殷皇子大馬路43-53A澳門廣場11樓K座&lt;/br&gt;行政支援查詢：澳門南灣羅保博士街1至3號國際銀行大廈6樓行政及財政處</t>
           </r>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2856 8288</t>
+            <t xml:space="preserve">科研資助查詢：(853) 2878 8777 &lt;/br&gt;行政支援查詢：(853) 2888 2088</t>
           </r>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2832 5432</t>
+            <t xml:space="preserve">科研資助查詢：(853) 2878 8775 / 2878 8776 &lt;/br&gt;行政支援查詢：(853) 2871 2552</t>
           </r>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">fdct@dsedt.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">https://fdct.dsedt.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12016,7 +12010,7 @@
       <c r="H62" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：黃善文
+            <t xml:space="preserve">行政管理委員會主席：余雨生
 </t>
           </r>
         </is>
@@ -12026,42 +12020,42 @@
       <c r="A63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">勞動債權保障基金</t>
+            <t xml:space="preserve">博彩委員會</t>
           </r>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門馬揸度博士大馬路221-279號先進廣場勞工事務局總辦事處</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 7822</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2852 5934</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@fgcl.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.fgcl.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -12069,14 +12063,6 @@
         <is>
           <r>
             <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">行政管理委員會主席：陳元童
-</t>
           </r>
         </is>
       </c>
@@ -12085,28 +12071,28 @@
       <c r="A64" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">博彩委員會</t>
+            <t xml:space="preserve">保安司</t>
           </r>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">澳門兵營斜巷</t>
           </r>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">（853）8799 7580</t>
           </r>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">（853）2871 5008</t>
           </r>
         </is>
       </c>
@@ -12120,7 +12106,7 @@
       <c r="F64" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">https://www.gss.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12128,6 +12114,15 @@
         <is>
           <r>
             <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">司長：陳子勁
+辦公室主任：林燕生
+</t>
           </r>
         </is>
       </c>
@@ -12136,7 +12131,7 @@
       <c r="A65" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">保安司</t>
+            <t xml:space="preserve">保安司司長辦公室</t>
           </r>
         </is>
       </c>
@@ -12185,7 +12180,7 @@
       <c r="H65" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">司長：陳子勁
+            <t xml:space="preserve">保安司司長：陳子勁
 辦公室主任：林燕生
 </t>
           </r>
@@ -12196,42 +12191,42 @@
       <c r="A66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">保安司司長辦公室</t>
+            <t xml:space="preserve">警察總局</t>
           </r>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門兵營斜巷</t>
+            <t xml:space="preserve">澳門南灣大馬路730-804號中華廣場7樓A-B座及16樓</t>
           </r>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8799 7580</t>
+            <t xml:space="preserve">（853）2871 2999,（853）8798 7510</t>
           </r>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 5008</t>
+            <t xml:space="preserve">（853）2871 3101</t>
           </r>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">info@spu.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.gss.gov.mo</t>
+            <t xml:space="preserve">https://www.spu.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12245,70 +12240,10 @@
       <c r="H66" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">保安司司長：陳子勁
-辦公室主任：林燕生
-</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">警察總局</t>
-          </r>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門南灣大馬路730-804號中華廣場7樓A-B座及16樓</t>
-          </r>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2871 2999,（853）8798 7510</t>
-          </r>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2871 3101</t>
-          </r>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">info@spu.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">https://www.spu.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <r>
             <t xml:space="preserve">局長：梁文昌
-局長助理：魏瑞斌
 局長助理：梁文照
 局長助理：林俊生
+代局長助理：李日明
 金融情報辦公室主任：朱婉儀
 辦公室協調員：趙汝民
 金融情報辦公室副主任：馮婉琪
@@ -12317,57 +12252,57 @@
         </is>
       </c>
     </row>
-    <row r="68" spans="1:8">
-      <c r="A68" t="inlineStr">
+    <row r="67" spans="1:8">
+      <c r="A67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">中華人民共和國澳門特別行政區海關</t>
           </r>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">澳門氹仔北安碼頭大馬路北安碼頭三巷澳門海關總部大樓</t>
           </r>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">（853）2855 9944</t>
           </r>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">（853）2837 1136</t>
           </r>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">info@customs.gov.mo</t>
           </r>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">http://www.customs.gov.mo</t>
           </r>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">156</t>
           </r>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">海關關長：何浩瀚
@@ -12379,82 +12314,84 @@
         </is>
       </c>
     </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">治安警察局</t>
+          </r>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">澳門氹仔北安碼頭大馬路治安警察局總部大樓</t>
+          </r>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2857 3333</t>
+          </r>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2878 0826</t>
+          </r>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">psp-info@fsm.gov.mo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">http://www.fsm.gov.mo/psp</t>
+          </r>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">局長：伍素萍
+代副局長：江偉俊
+代副局長：黃劍虹
+代副局長：陳溥棠
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
     <row r="69" spans="1:8">
       <c r="A69" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">治安警察局</t>
+            <t xml:space="preserve">司法警察局</t>
           </r>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門氹仔北安碼頭大馬路治安警察局總部大樓</t>
+            <t xml:space="preserve">澳門友誼大馬路 823號司法警察局大樓（總部）</t>
           </r>
         </is>
       </c>
       <c r="C69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2857 3333</t>
-          </r>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2878 0826</t>
-          </r>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">psp-info@fsm.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">http://www.fsm.gov.mo/psp</t>
-          </r>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">代局長：伍素萍
-代副局長：鄭俊禧
-</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">司法警察局</t>
-          </r>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門友誼大馬路 823號司法警察局大樓（總部）</t>
-          </r>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">總機：（853）2855 7777 
@@ -12462,35 +12399,35 @@
           </r>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2831 2780 </t>
-          </r>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">nar@pj.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="D69" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2831 2780</t>
+          </r>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">sfdtr@pj.gov.mo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">http://www.pj.gov.mo</t>
           </r>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">局長：薛仲明
@@ -12502,47 +12439,109 @@
         </is>
       </c>
     </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">消防局</t>
+          </r>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">澳門何鴻燊博士大馬路</t>
+          </r>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">緊急求助電話：119，120，（853）2857 2222 
+ 查詢及投訴：（853）8989 1373，（853）8989 1374（設有電話同步錄音）</t>
+          </r>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2836 1128</t>
+          </r>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">cb-info@fsm.gov.mo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">http://www.fsm.gov.mo/cb</t>
+          </r>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">局長：王健
+副局長：張智宏
+副局長：李龍傑
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
     <row r="71" spans="1:8">
       <c r="A71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">消防局</t>
+            <t xml:space="preserve">懲教管理局</t>
           </r>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門何鴻燊博士大馬路</t>
+            <t xml:space="preserve">澳門路環九澳堤壩馬路</t>
           </r>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">緊急求助電話：119，120，（853）2857 2222 
- 查詢及投訴：（853）8989 1373，（853）8989 1374（設有電話同步錄音）</t>
+            <t xml:space="preserve">總機：（853）2888 1211 
+查詢及投訴：（853）8896 1280，（853）8896 1283（設有電話錄音）</t>
           </r>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2836 1128</t>
+            <t xml:space="preserve">（853）2888 2431</t>
           </r>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">cb-info@fsm.gov.mo</t>
+            <t xml:space="preserve">info@dsc.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.fsm.gov.mo/cb</t>
+            <t xml:space="preserve">http://www.dsc.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12556,9 +12555,8 @@
       <c r="H71" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">局長：王健
-副局長：張智宏
-代副局長：李龍傑
+            <t xml:space="preserve">代局長：李昶文
+代副局長：呂錦雲
 </t>
           </r>
         </is>
@@ -12568,7 +12566,7 @@
       <c r="A72" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">懲教管理局</t>
+            <t xml:space="preserve">路環監獄</t>
           </r>
         </is>
       </c>
@@ -12582,8 +12580,7 @@
       <c r="C72" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">總機：（853）2888 1211 
-查詢及投訴：（853）8896 1280，（853）8896 1283（設有電話錄音）</t>
+            <t xml:space="preserve">（853）2888 1211</t>
           </r>
         </is>
       </c>
@@ -12612,15 +12609,6 @@
         <is>
           <r>
             <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">局長：程况明
-副局長：李日明
-</t>
           </r>
         </is>
       </c>
@@ -12629,35 +12617,35 @@
       <c r="A73" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">路環監獄</t>
+            <t xml:space="preserve">少年感化院</t>
           </r>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門路環九澳堤壩馬路</t>
+            <t xml:space="preserve">澳門路環竹灣馬路1號</t>
           </r>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 1211</t>
+            <t xml:space="preserve">（853）2888 2439,（853）8899 3109</t>
           </r>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 2431</t>
+            <t xml:space="preserve">（853）2888 0178</t>
           </r>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@dsc.gov.mo</t>
+            <t xml:space="preserve">im@dsc.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12680,35 +12668,35 @@
       <c r="A74" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">少年感化院</t>
+            <t xml:space="preserve">懲教管理局服務諮詢中心</t>
           </r>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門路環竹灣馬路1號</t>
+            <t xml:space="preserve">澳門南灣大馬路762-804號中華廣場8樓A座</t>
           </r>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 2439,（853）8899 3109</t>
+            <t xml:space="preserve">（853）2871 5800</t>
           </r>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 0178</t>
+            <t xml:space="preserve">（853）2871 5355</t>
           </r>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">im@dsc.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -12731,42 +12719,42 @@
       <c r="A75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">懲教管理局服務諮詢中心</t>
+            <t xml:space="preserve">澳門保安部隊事務局</t>
           </r>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門南灣大馬路762-804號中華廣場8樓A座</t>
+            <t xml:space="preserve">澳門何賢紳士大馬路政府(青茂)辦公大樓8樓</t>
           </r>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 5800</t>
+            <t xml:space="preserve">（853）2855 9999</t>
           </r>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 5355</t>
+            <t xml:space="preserve">（853）2855 9998</t>
           </r>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">info@fsm.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.dsc.gov.mo</t>
+            <t xml:space="preserve">http://www.fsm.gov.mo/dsfsm</t>
           </r>
         </is>
       </c>
@@ -12777,58 +12765,7 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門保安部隊事務局</t>
-          </r>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門何賢紳士大馬路政府(青茂)辦公大樓8樓</t>
-          </r>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2855 9999</t>
-          </r>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">（853）2855 9998</t>
-          </r>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">info@fsm.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">http://www.fsm.gov.mo/dsfsm</t>
-          </r>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">局長：劉運嫦
@@ -12839,46 +12776,106 @@
         </is>
       </c>
     </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">澳門保安部隊高等學校</t>
+          </r>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">澳門路環石街</t>
+          </r>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2887 1112 </t>
+          </r>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2887 1117,（853）8899 0589</t>
+          </r>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">esfsm-info@fsm.gov.mo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">http://www.fsm.gov.mo/esfsm </t>
+          </r>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">校長：黃子暉
+副校長：林曉帆
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
     <row r="77" spans="1:8">
       <c r="A77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門保安部隊高等學校</t>
+            <t xml:space="preserve">懲教基金</t>
           </r>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門路環石街</t>
+            <t xml:space="preserve">澳門路環九澳堤壩馬路</t>
           </r>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2887 1112 </t>
+            <t xml:space="preserve">（853）2888 1211（總機）</t>
           </r>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2887 1117,（853）8899 0589</t>
+            <t xml:space="preserve">（853）2888 2431</t>
           </r>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">esfsm-info@fsm.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.fsm.gov.mo/esfsm </t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -12892,8 +12889,7 @@
       <c r="H77" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">校長：黃子暉
-副校長：林曉帆
+            <t xml:space="preserve">行政管理委員會主席：李昶文
 </t>
           </r>
         </is>
@@ -12903,35 +12899,35 @@
       <c r="A78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">懲教基金</t>
+            <t xml:space="preserve">海關福利會</t>
           </r>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門路環九澳堤壩馬路</t>
+            <t xml:space="preserve">氹仔北安碼頭大馬路北安碼頭三巷澳門海關總部大樓</t>
           </r>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 1211（總機）</t>
+            <t xml:space="preserve">（853）8833 6894</t>
           </r>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2888 2431</t>
+            <t xml:space="preserve">（853）8833 6893</t>
           </r>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">ossa@customs.gov.mo</t>
           </r>
         </is>
       </c>
@@ -12952,7 +12948,8 @@
       <c r="H78" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：程况明
+            <t xml:space="preserve">行政委員會主席：何浩瀚
+行政委員會副主席：李煜輝
 </t>
           </r>
         </is>
@@ -12962,35 +12959,35 @@
       <c r="A79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">海關福利會</t>
+            <t xml:space="preserve">治安警察局福利會</t>
           </r>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">氹仔北安碼頭大馬路北安碼頭三巷澳門海關總部大樓</t>
+            <t xml:space="preserve">澳門羅德禮將軍街2號福利會大廈地下D</t>
           </r>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8833 6894</t>
+            <t xml:space="preserve">(853) 87905450 / 87905451</t>
           </r>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8833 6893</t>
+            <t xml:space="preserve">（853）2837 2025</t>
           </r>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">ossa@customs.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -13011,8 +13008,8 @@
       <c r="H79" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政委員會主席：何浩瀚
-行政委員會副主席：李煜輝
+            <t xml:space="preserve">行政管理委員會主席：伍素萍
+行政管理委員會副主席：江偉俊
 </t>
           </r>
         </is>
@@ -13022,35 +13019,35 @@
       <c r="A80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">治安警察局福利會</t>
+            <t xml:space="preserve">司法警察局福利會</t>
           </r>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門羅德禮將軍街2號福利會大廈地下D</t>
+            <t xml:space="preserve">澳門友誼大馬路 823號司法警察局大樓（總部）</t>
           </r>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">(853) 87905450 / 87905451</t>
+            <t xml:space="preserve">（853）8800 1691</t>
           </r>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2837 2025</t>
+            <t xml:space="preserve">（853）8800 6360</t>
           </r>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">ospj@pj.gov.mo</t>
           </r>
         </is>
       </c>
@@ -13071,7 +13068,8 @@
       <c r="H80" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：伍素萍
+            <t xml:space="preserve">行政管理委員會主席：薛仲明
+行政管理委員會副主席：岑錦榮
 </t>
           </r>
         </is>
@@ -13081,35 +13079,35 @@
       <c r="A81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">司法警察局福利會</t>
+            <t xml:space="preserve">消防局福利會</t>
           </r>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門友誼大馬路 823號司法警察局大樓（總部）</t>
+            <t xml:space="preserve">澳門何鴻燊博士大馬路</t>
           </r>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8800 1691</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8800 6360</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">ospj@pj.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -13130,8 +13128,8 @@
       <c r="H81" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：薛仲明
-行政管理委員會副主席：岑錦榮
+            <t xml:space="preserve">行政管理委員會主席：王健
+行政管理委員會副主席：張智宏
 </t>
           </r>
         </is>
@@ -13141,42 +13139,43 @@
       <c r="A82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">消防局福利會</t>
+            <t xml:space="preserve">阻嚇販賣人口措施關注委員會</t>
           </r>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門何鴻燊博士大馬路</t>
+            <t xml:space="preserve">澳門兵營斜巷</t>
           </r>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">24小時舉報及求助熱線：（853）2888 9911 
+ 辦公室電話：（853）8799 7102</t>
           </r>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">（853）2871 5008</t>
           </r>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">info@anti-tip.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">https://www.anti-tip.gov.mo</t>
           </r>
         </is>
       </c>
@@ -13190,8 +13189,7 @@
       <c r="H82" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：王健
-行政管理委員會副主席：張智宏
+            <t xml:space="preserve">協調員：林燕生
 </t>
           </r>
         </is>
@@ -13201,43 +13199,42 @@
       <c r="A83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">阻嚇販賣人口措施關注委員會</t>
+            <t xml:space="preserve">社會文化司</t>
           </r>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門兵營斜巷</t>
+            <t xml:space="preserve">澳門風順堂街28號政府總部2樓</t>
           </r>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24小時舉報及求助熱線：（853）2888 9911 
- 辦公室電話：（853）8799 7102</t>
+            <t xml:space="preserve">（853）2872 6886 </t>
           </r>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 5008</t>
+            <t xml:space="preserve">（853）2872 7594 </t>
           </r>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@anti-tip.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.anti-tip.gov.mo</t>
+            <t xml:space="preserve">http://www.gsasc.gov.mo</t>
           </r>
         </is>
       </c>
@@ -13251,7 +13248,8 @@
       <c r="H83" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">協調員：林燕生
+            <t xml:space="preserve">司長：柯嵐
+辦公室主任：林媛
 </t>
           </r>
         </is>
@@ -13261,7 +13259,7 @@
       <c r="A84" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">社會文化司</t>
+            <t xml:space="preserve">社會文化司司長辦公室</t>
           </r>
         </is>
       </c>
@@ -13310,7 +13308,7 @@
       <c r="H84" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">司長：柯嵐
+            <t xml:space="preserve">社會文化司司長：柯嵐
 辦公室主任：林媛
 </t>
           </r>
@@ -13321,42 +13319,42 @@
       <c r="A85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">社會文化司司長辦公室</t>
+            <t xml:space="preserve">教育及青年發展局</t>
           </r>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門風順堂街28號政府總部2樓</t>
+            <t xml:space="preserve">澳門約翰四世大馬路7-9號1樓</t>
           </r>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2872 6886 </t>
+            <t xml:space="preserve">（853）2855 5533</t>
           </r>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2872 7594 </t>
+            <t xml:space="preserve">（853）2871 1294</t>
           </r>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">webmaster@dsedj.gov.mo</t>
           </r>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.gsasc.gov.mo</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo</t>
           </r>
         </is>
       </c>
@@ -13370,8 +13368,10 @@
       <c r="H85" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">社會文化司司長：柯嵐
-辦公室主任：林媛
+            <t xml:space="preserve">局長：龔志明
+副局長：阮佩賢
+副局長：黃嘉祺
+代副局長：蔡敏芝
 </t>
           </r>
         </is>
@@ -13381,7 +13381,7 @@
       <c r="A86" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">教育及青年發展局</t>
+            <t xml:space="preserve">教育宣傳及公關中心</t>
           </r>
         </is>
       </c>
@@ -13409,14 +13409,14 @@
       <c r="E86" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">webmaster@dsedj.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -13424,17 +13424,6 @@
         <is>
           <r>
             <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">局長：龔志明
-副局長：丁少雄
-副局長：阮佩賢
-副局長：黃嘉祺
-</t>
           </r>
         </is>
       </c>
@@ -13443,28 +13432,28 @@
       <c r="A87" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">教育宣傳及公關中心</t>
+            <t xml:space="preserve">德育中心</t>
           </r>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門約翰四世大馬路7-9號1樓</t>
+            <t xml:space="preserve">澳門祐漢看台街 313號翡翠廣場 3樓</t>
           </r>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2855 5533</t>
+            <t xml:space="preserve">（853）2840 3200</t>
           </r>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2871 1294</t>
+            <t xml:space="preserve">（853）2840 3440</t>
           </r>
         </is>
       </c>
@@ -13478,7 +13467,7 @@
       <c r="F87" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cem</t>
           </r>
         </is>
       </c>
@@ -13494,28 +13483,28 @@
       <c r="A88" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">德育中心</t>
+            <t xml:space="preserve">教育資源中心</t>
           </r>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門祐漢看台街 313號翡翠廣場 3樓</t>
+            <t xml:space="preserve">澳門南灣大馬路926號</t>
           </r>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 3200</t>
+            <t xml:space="preserve">（853）8395 9200</t>
           </r>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 3440</t>
+            <t xml:space="preserve">（853）2837 0448, （853）8395 9131</t>
           </r>
         </is>
       </c>
@@ -13529,7 +13518,7 @@
       <c r="F88" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cem</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cre</t>
           </r>
         </is>
       </c>
@@ -13545,28 +13534,28 @@
       <c r="A89" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">教育資源中心</t>
+            <t xml:space="preserve">教育心理輔導及特殊教育中心</t>
           </r>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門南灣大馬路926號</t>
+            <t xml:space="preserve">澳門美麗街31號2樓及4樓</t>
           </r>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8395 9200</t>
+            <t xml:space="preserve">（853）2840 1010</t>
           </r>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2837 0448, （853）8395 9131</t>
+            <t xml:space="preserve">（853）2840 0801，（853）2835 5210</t>
           </r>
         </is>
       </c>
@@ -13580,7 +13569,7 @@
       <c r="F89" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cre</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/capee</t>
           </r>
         </is>
       </c>
@@ -13596,28 +13585,28 @@
       <c r="A90" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">教育心理輔導及特殊教育中心</t>
+            <t xml:space="preserve">語言推廣中心</t>
           </r>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門美麗街31號2樓及4樓</t>
+            <t xml:space="preserve">澳門美麗街31號3樓</t>
           </r>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 1010</t>
+            <t xml:space="preserve">（853）2840 0211</t>
           </r>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 0801，（853）2835 5210</t>
+            <t xml:space="preserve">（853）2840 0615</t>
           </r>
         </is>
       </c>
@@ -13631,7 +13620,7 @@
       <c r="F90" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/capee</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cdl</t>
           </r>
         </is>
       </c>
@@ -13647,28 +13636,28 @@
       <c r="A91" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">語言推廣中心</t>
+            <t xml:space="preserve">親職教育中心</t>
           </r>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門美麗街31號3樓</t>
+            <t xml:space="preserve">澳門氹仔布拉干薩街濠景花園24 - 26座地下</t>
           </r>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 0211</t>
+            <t xml:space="preserve">（853）2884 1284</t>
           </r>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2840 0615</t>
+            <t xml:space="preserve">（853）2884 1290</t>
           </r>
         </is>
       </c>
@@ -13682,7 +13671,7 @@
       <c r="F91" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cdl</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cep</t>
           </r>
         </is>
       </c>
@@ -13698,28 +13687,28 @@
       <c r="A92" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">親職教育中心</t>
+            <t xml:space="preserve">青年試館</t>
           </r>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門氹仔布拉干薩街濠景花園24 - 26座地下</t>
+            <t xml:space="preserve">澳門高偉樂街（塔石體育館）</t>
           </r>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2884 1284</t>
+            <t xml:space="preserve">（853）2833 2084</t>
           </r>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2884 1290</t>
+            <t xml:space="preserve">（853）2853 0418</t>
           </r>
         </is>
       </c>
@@ -13733,7 +13722,7 @@
       <c r="F92" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cep</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cej.php</t>
           </r>
         </is>
       </c>
@@ -13749,28 +13738,28 @@
       <c r="A93" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">青年試館</t>
+            <t xml:space="preserve">外港活動中心</t>
           </r>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門高偉樂街（塔石體育館）</t>
+            <t xml:space="preserve">澳門新口岸畢仕達大馬路綜藝館第2座</t>
           </r>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2833 2084</t>
+            <t xml:space="preserve">（853）2870 1385，（853）2870 1386</t>
           </r>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2853 0418</t>
+            <t xml:space="preserve">（853）2870 1387</t>
           </r>
         </is>
       </c>
@@ -13784,7 +13773,7 @@
       <c r="F93" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cej.php</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cape.php</t>
           </r>
         </is>
       </c>
@@ -13800,28 +13789,28 @@
       <c r="A94" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">外港活動中心</t>
+            <t xml:space="preserve">駿菁活動中心</t>
           </r>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門新口岸畢仕達大馬路綜藝館第2座</t>
+            <t xml:space="preserve">澳門順景廣場（近馬場東大馬路）</t>
           </r>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2870 1385，（853）2870 1386</t>
+            <t xml:space="preserve">（853）2842 5110, （853）2842 5112</t>
           </r>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2870 1387</t>
+            <t xml:space="preserve">（853）2842 5900</t>
           </r>
         </is>
       </c>
@@ -13835,7 +13824,7 @@
       <c r="F94" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cape.php</t>
+            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cabh.php</t>
           </r>
         </is>
       </c>
@@ -13851,28 +13840,28 @@
       <c r="A95" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">駿菁活動中心</t>
+            <t xml:space="preserve">澳門演藝學院附屬教育中心</t>
           </r>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門順景廣場（近馬場東大馬路）</t>
+            <t xml:space="preserve">澳門高士德大馬路14-16號</t>
           </r>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2842 5110, （853）2842 5112</t>
+            <t xml:space="preserve">（853）2857 1230</t>
           </r>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2842 5900</t>
+            <t xml:space="preserve">（853）2852 3483</t>
           </r>
         </is>
       </c>
@@ -13886,7 +13875,7 @@
       <c r="F95" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">https://www.dsedj.gov.mo/cj/index-cabh.php</t>
+            <t xml:space="preserve">https://portal.dsedj.gov.mo/webdsejspace/cons/Inter_main_page.jsp</t>
           </r>
         </is>
       </c>
@@ -14259,53 +14248,104 @@
       <c r="A103" t="inlineStr">
         <is>
           <r>
+            <t xml:space="preserve">澳門演藝學院</t>
+          </r>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">澳門高士德大馬路14-16號</t>
+          </r>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2857 1207</t>
+          </r>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）2852 3483</t>
+          </r>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">https://portal.dsedj.gov.mo/webdsejspace/cons/Inter_main_page.jsp</t>
+          </r>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">文化局</t>
           </r>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">澳門塔石廣場文化局大樓</t>
           </r>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">（853）2836 6866</t>
           </r>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">（853）2836 6899</t>
           </r>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">webmaster@icm.gov.mo</t>
           </r>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">http://www.icm.gov.mo</t>
           </r>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="G104" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">局長：梁惠敏
@@ -14316,66 +14356,6 @@
         </is>
       </c>
     </row>
-    <row r="104" spans="1:8">
-      <c r="A104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門演藝學院</t>
-          </r>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門演藝學院：澳門高士德大馬路14-16號
-舞蹈學校︰澳門路環紅荷路108號政府（路環）辦公大樓6樓
-音樂學校︰澳門和隆街35號（望德堂對面）
-戲劇學校：澳門友誼大馬路海景花園新安花園87 號U</t>
-          </r>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門演藝學院：（853）2857 1207 
-舞蹈學校：（853）2875 0562 
- 音樂學校：（853）2835 2766 
-戲劇學校：（853）2870 1588</t>
-          </r>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">澳門演藝學院：（853）2852 3483 
-舞蹈學校：（853）2875 0568 
-音樂學校：（853）2835 2700 
-戲劇學校：（853）2870 1568</t>
-          </r>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">info.cm@icm.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">http://www.cons.gov.mo</t>
-          </r>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"/>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="105" spans="1:8">
       <c r="A105" t="inlineStr">
         <is>
@@ -16673,9 +16653,9 @@
       <c r="H149" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">代局長：李詩靈
+            <t xml:space="preserve">局長：梁惠敏
+副局長：李詩靈
 副局長：鄭繼明
-副局長：---
 </t>
           </r>
         </is>
@@ -16737,7 +16717,7 @@
             <t xml:space="preserve">局長：羅奕龍
 副局長：鄭成業
 副局長：陳永華
-代副局長：戴華浩（仁伯爵綜合醫院代院長）
+副局長：戴華浩（仁伯爵綜合醫院院長）
 </t>
           </r>
         </is>
@@ -17930,10 +17910,10 @@
         <is>
           <r>
             <t xml:space="preserve">院長：劉正印
-副院長：李偉成
-副院長：李莉
+副院長：柳曉輝
+副院長：胡冰水
 副院長：孫國強
-職位等同副院長級別的人員：柳曉輝
+職位等同副院長級別的人員：趙穎
 職位等同副院長級別的人員：沈寧
 </t>
           </r>
@@ -17995,7 +17975,7 @@
           <r>
             <t xml:space="preserve">局長：韓衛
 副局長：許華寶
-副局長：鄧玉華
+副局長：丁少雄
 </t>
           </r>
         </is>
@@ -18857,7 +18837,7 @@
             <t xml:space="preserve">校長：周仲榮
 副校長：羅曼儀
 副校長：---
-秘書長：莫秀妍
+代秘書長：甄嘉瑩
 </t>
           </r>
         </is>
@@ -19036,7 +19016,7 @@
       <c r="H193" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">行政管理委員會主席：李詩靈
+            <t xml:space="preserve">行政管理委員會主席：梁惠敏
 </t>
           </r>
         </is>
@@ -19945,8 +19925,8 @@
         <is>
           <r>
             <t xml:space="preserve">局長：鄭岳威
-副局長：李頴康
 副局長：莫垂道
+代副局長：雅永健
 </t>
           </r>
         </is>
@@ -21677,21 +21657,21 @@
       <c r="B240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門南灣大馬路459號</t>
           </r>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8398 4117 </t>
+            <t xml:space="preserve">（853）8298 4117</t>
           </r>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2832 6744 </t>
+            <t xml:space="preserve">（853）2832 6744</t>
           </r>
         </is>
       </c>
@@ -21738,7 +21718,7 @@
       <c r="B241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門四月二十五日前地</t>
           </r>
         </is>
       </c>
@@ -21752,7 +21732,7 @@
       <c r="D241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2832 6747 </t>
+            <t xml:space="preserve">（853）2832 6747</t>
           </r>
         </is>
       </c>
@@ -21766,7 +21746,7 @@
       <c r="F241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.court.gov.mo </t>
+            <t xml:space="preserve">https://www.court.gov.mo</t>
           </r>
         </is>
       </c>
@@ -21780,7 +21760,7 @@
       <c r="H241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">院長：蔡武彬
+            <t xml:space="preserve">院長：盛銳敏
 </t>
           </r>
         </is>
@@ -22270,14 +22250,14 @@
       <c r="B251" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門湖畔南街中國與葡語國家商貿合作服務平台綜合體辦公樓2樓</t>
+            <t xml:space="preserve">澳門龍嵩正街9-A號</t>
           </r>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8398 4136</t>
+            <t xml:space="preserve">（853）8298 4136</t>
           </r>
         </is>
       </c>
@@ -22544,7 +22524,7 @@
       <c r="B256" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門南灣大馬路459號</t>
           </r>
         </is>
       </c>
@@ -22558,7 +22538,7 @@
       <c r="D256" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2836 5214</t>
+            <t xml:space="preserve">（853）2850 9183</t>
           </r>
         </is>
       </c>
@@ -22595,7 +22575,7 @@
       <c r="B257" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
           </r>
         </is>
       </c>
@@ -23350,14 +23330,14 @@
       <c r="C270" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2885 0065 </t>
+            <t xml:space="preserve">（853）2885 0065</t>
           </r>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2885 0083 </t>
+            <t xml:space="preserve">（853）2885 0083</t>
           </r>
         </is>
       </c>
@@ -23371,7 +23351,7 @@
       <c r="F270" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">https://www.csrmacau.com.mo</t>
           </r>
         </is>
       </c>
@@ -24538,7 +24518,8 @@
       <c r="B290" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門俾利喇街157號A</t>
+            <t xml:space="preserve">澳門俾利喇街157號A
+澳門路環紅荷路108號政府(路環)辦公大樓10樓</t>
           </r>
         </is>
       </c>
@@ -24581,10 +24562,10 @@
         <is>
           <r>
             <t xml:space="preserve">執行委員會主席：羅崇雯
-委員：馬錦強
 委員：袁泳貴
 委員：黃偉鴻
 委員：鄭光普
+委員：李從正
 </t>
           </r>
         </is>
@@ -25062,7 +25043,7 @@
       <c r="H298" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">董事長：嚴肇基
+            <t xml:space="preserve">董事長：羅曼儀
 </t>
           </r>
         </is>
@@ -25305,6 +25286,67 @@
             <t xml:space="preserve">董事長：謝永強
 董事：譚致寧
 董事：陳祖榮
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">廣東橫琴粵澳深度合作區澳理大高等教育發展有限公司</t>
+          </r>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">珠海市橫琴港澳大道868號市民服務中心2號樓政務服務中心114室-3343（集中辦公區）</t>
+          </r>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">（853）8599 6765</t>
+          </r>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">mpuhed@mpu.edu.mo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">董事長：周仲榮
+董事：張詠藍
+董事：林逸文
 </t>
           </r>
         </is>

--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1523">
   <si>
     <r>
       <t xml:space="preserve">行政長官</t>
@@ -5500,7 +5500,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門鴨涌馬路220號青葱大廈地下L</t>
+      <t xml:space="preserve">澳門沙梨頭北街238號</t>
     </r>
   </si>
   <si>
@@ -5510,7 +5510,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2830 5909</t>
+      <t xml:space="preserve">（853）8299 4222</t>
     </r>
   </si>
   <si>
@@ -5520,7 +5520,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">http://www.ihm.gov.mo</t>
+      <t xml:space="preserve">https://www.ihm.gov.mo</t>
     </r>
   </si>
   <si>
@@ -5595,6 +5595,21 @@
   <si>
     <r>
       <t xml:space="preserve">樓宇維修基金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">澳門鴨涌馬路220號青葱大廈地下L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2830 5909</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">http://www.ihm.gov.mo</t>
     </r>
   </si>
   <si>
@@ -20064,7 +20079,7 @@
       <c r="B212" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門鴨涌馬路220號青葱大廈地下L</t>
+            <t xml:space="preserve">澳門沙梨頭北街238號</t>
           </r>
         </is>
       </c>
@@ -20078,7 +20093,7 @@
       <c r="D212" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2830 5909</t>
+            <t xml:space="preserve">（853）8299 4222</t>
           </r>
         </is>
       </c>
@@ -20092,7 +20107,7 @@
       <c r="F212" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">http://www.ihm.gov.mo</t>
+            <t xml:space="preserve">https://www.ihm.gov.mo</t>
           </r>
         </is>
       </c>

--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -1876,12 +1876,15 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2855 9944</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2837 1136</t>
+      <t xml:space="preserve">緊急求助熱線：116 
+查詢、舉報及投訴熱線：（853）2896 5001 
+海關總部電話：（853）2855 9944</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2837 1136 
+（853）2896 5003</t>
     </r>
   </si>
   <si>
@@ -1896,7 +1899,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">156</t>
+      <t xml:space="preserve">澳門郵政信箱156</t>
     </r>
   </si>
   <si>
@@ -5940,7 +5943,6 @@
     <r>
       <t xml:space="preserve">秘書長：林智龍
 副秘書長：潘錦屏
-副秘書長：---
 </t>
     </r>
   </si>
@@ -12285,14 +12287,17 @@
       <c r="C67" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2855 9944</t>
+            <t xml:space="preserve">緊急求助熱線：116 
+查詢、舉報及投訴熱線：（853）2896 5001 
+海關總部電話：（853）2855 9944</t>
           </r>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2837 1136</t>
+            <t xml:space="preserve">（853）2837 1136 
+（853）2896 5003</t>
           </r>
         </is>
       </c>
@@ -12313,7 +12318,7 @@
       <c r="G67" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">156</t>
+            <t xml:space="preserve">澳門郵政信箱156</t>
           </r>
         </is>
       </c>
@@ -21095,7 +21100,6 @@
           <r>
             <t xml:space="preserve">秘書長：林智龍
 副秘書長：潘錦屏
-副秘書長：---
 </t>
           </r>
         </is>

--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1521">
   <si>
     <r>
       <t xml:space="preserve">行政長官</t>
@@ -5598,16 +5598,6 @@
   <si>
     <r>
       <t xml:space="preserve">樓宇維修基金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門鴨涌馬路220號青葱大廈地下L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2830 5909</t>
     </r>
   </si>
   <si>
@@ -20267,7 +20257,7 @@
       <c r="B215" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門鴨涌馬路220號青葱大廈地下L</t>
+            <t xml:space="preserve">澳門沙梨頭北街238號</t>
           </r>
         </is>
       </c>
@@ -20281,7 +20271,7 @@
       <c r="D215" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2830 5909</t>
+            <t xml:space="preserve">（853）8299 4222</t>
           </r>
         </is>
       </c>

--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1520">
   <si>
     <r>
       <t xml:space="preserve">行政長官</t>
@@ -6436,17 +6436,17 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">澳門南灣大馬路517號南通商業大廈22樓B-C座</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2835 6060 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2835 5593 </t>
+      <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2835 6060</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2835 5593</t>
     </r>
   </si>
   <si>
@@ -6577,11 +6577,6 @@
   <si>
     <r>
       <t xml:space="preserve">檢察院駐中級法院辦事處</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
     </r>
   </si>
   <si>
@@ -22208,21 +22203,21 @@
       <c r="B250" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門南灣大馬路517號南通商業大廈22樓B-C座</t>
+            <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
           </r>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2835 6060 </t>
+            <t xml:space="preserve">（853）2835 6060</t>
           </r>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2835 5593 </t>
+            <t xml:space="preserve">（853）2835 5593</t>
           </r>
         </is>
       </c>

--- a/Rawdata/msar-apm-entities-contact-zh.xlsx
+++ b/Rawdata/msar-apm-entities-contact-zh.xlsx
@@ -164,17 +164,24 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2896 6777</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）2896 8658</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">info@fm.org.mo</t>
+      <t xml:space="preserve">（853）8795-0950（諮詢、建議、投訴、舉報及非緊急求助）
+（853）2896-6777（其他事宜）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）8988-0299（諮詢、建議、投訴、舉報及非緊急求助）
+（853）2896-8658（總務）
+（853）2835-6016（資助監察處）
+（853）2872-5688（活動處）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">opinion@fm.org.mo（諮詢、建議、投訴、舉報及非緊急求助）
+ info@fm.org.mo（總務）
+ dfaf_info@fm.org.mo（資助監察處）
+ da_info@fm.org.mo（活動處）</t>
     </r>
   </si>
   <si>
@@ -197,6 +204,11 @@
   <si>
     <r>
       <t xml:space="preserve">澳門新口岸新填海區宋玉生廣場403至439號澳門教科文中心</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2896 6777</t>
     </r>
   </si>
   <si>
@@ -6483,32 +6495,32 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">（853）8298 4397</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">（853）2896 3967</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">www.court.gov.mo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">法官委員會</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">法律代辦紀律權限獨立委員會</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">（853）8398 4397</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">www.court.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">法官委員會</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">edoc_cmj@court.gov.mo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">法律代辦紀律權限獨立委員會</t>
     </r>
   </si>
   <si>
@@ -6592,28 +6604,23 @@
   <si>
     <r>
       <t xml:space="preserve">接待及一般查詢：澳門殷皇子大馬路47-53號澳門廣場3樓
-民事及勞動範疇：澳門殷皇子大馬路47-53號澳門廣場3樓及4樓
+民事、家事及勞動範疇：澳門殷皇子大馬路47-53號澳門廣場3樓（民事及家事科）及4樓（勞動科）
 刑事範疇：澳門何鴻燊博士大馬路347號初級法院刑事大樓1樓</t>
     </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">（853）2855 7714</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">接待及一般查詢、民事及勞動範疇：（853）2833 9501&lt;/br&gt;刑事範疇：（853）2853 2441</t>
+      <t xml:space="preserve">接待及一般查詢：（853）2855 7714&lt;/br&gt;民事、家事及勞動範疇：（853）2855 7714&lt;/br&gt;刑事範疇：（853）8506 5100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">接待及一般查詢：（853）2833 9501&lt;/br&gt;民事、家事及勞動範疇：（853）2833 9501&lt;/br&gt;刑事範疇：（853）2853 2441</t>
     </r>
   </si>
   <si>
     <r>
       <t xml:space="preserve">檢察院駐行政法院辦事處</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">澳門南灣大馬路517號南通商業大廈22樓A座</t>
     </r>
   </si>
   <si>
@@ -8679,21 +8686,28 @@
       <c r="C6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2896 6777</t>
+            <t xml:space="preserve">（853）8795-0950（諮詢、建議、投訴、舉報及非緊急求助）
+（853）2896-6777（其他事宜）</t>
           </r>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2896 8658</t>
+            <t xml:space="preserve">（853）8988-0299（諮詢、建議、投訴、舉報及非緊急求助）
+（853）2896-8658（總務）
+（853）2835-6016（資助監察處）
+（853）2872-5688（活動處）</t>
           </r>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">info@fm.org.mo</t>
+            <t xml:space="preserve">opinion@fm.org.mo（諮詢、建議、投訴、舉報及非緊急求助）
+ info@fm.org.mo（總務）
+ dfaf_info@fm.org.mo（資助監察處）
+ da_info@fm.org.mo（活動處）</t>
           </r>
         </is>
       </c>
@@ -22314,21 +22328,21 @@
       <c r="B252" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門南灣大馬路459號</t>
           </r>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8398 4397</t>
+            <t xml:space="preserve">（853）8298 4397</t>
           </r>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">（853）2896 3967</t>
           </r>
         </is>
       </c>
@@ -22365,28 +22379,28 @@
       <c r="B253" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門四月二十五日前地終審及中級法院大樓</t>
+            <t xml:space="preserve">澳門南灣大馬路459號</t>
           </r>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）8398 4397</t>
+            <t xml:space="preserve">（853）8298 4397</t>
           </r>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"/>
+            <t xml:space="preserve">（853）2896 3967</t>
           </r>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">edoc_cmj@court.gov.mo</t>
+            <t xml:space="preserve"/>
           </r>
         </is>
       </c>
@@ -22631,7 +22645,7 @@
         <is>
           <r>
             <t xml:space="preserve">接待及一般查詢：澳門殷皇子大馬路47-53號澳門廣場3樓
-民事及勞動範疇：澳門殷皇子大馬路47-53號澳門廣場3樓及4樓
+民事、家事及勞動範疇：澳門殷皇子大馬路47-53號澳門廣場3樓（民事及家事科）及4樓（勞動科）
 刑事範疇：澳門何鴻燊博士大馬路347號初級法院刑事大樓1樓</t>
           </r>
         </is>
@@ -22639,14 +22653,14 @@
       <c r="C258" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">（853）2855 7714</t>
+            <t xml:space="preserve">接待及一般查詢：（853）2855 7714&lt;/br&gt;民事、家事及勞動範疇：（853）2855 7714&lt;/br&gt;刑事範疇：（853）8506 5100</t>
           </r>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">接待及一般查詢、民事及勞動範疇：（853）2833 9501&lt;/br&gt;刑事範疇：（853）2853 2441</t>
+            <t xml:space="preserve">接待及一般查詢：（853）2833 9501&lt;/br&gt;民事、家事及勞動範疇：（853）2833 9501&lt;/br&gt;刑事範疇：（853）2853 2441</t>
           </r>
         </is>
       </c>
@@ -22683,7 +22697,7 @@
       <c r="B259" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">澳門南灣大馬路517號南通商業大廈22樓A座</t>
+            <t xml:space="preserve">澳門四月二十五日前地中級法院大樓</t>
           </r>
         </is>
       </c>
